--- a/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Evidence & Assumptions Log.xlsx
+++ b/PROYECTO_CIGARS_CUBA_2027/09_RESEARCH/Evidence & Assumptions Log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="118">
   <si>
     <t xml:space="preserve">Registro de evidencias y supuestos</t>
   </si>
@@ -326,6 +326,36 @@
   </si>
   <si>
     <t xml:space="preserve">Asesor andorrano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No se halló marca de puros «Arnaldo» en búsqueda web preliminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informe de registrabilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegas Robaina (nombre de veguero) es marca de Habanos S.A. desde 1997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arnaldo consiente el uso de su nombre y su empleador lo autoriza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reunión R1 + abogado cubano</t>
   </si>
   <si>
     <t xml:space="preserve">E25</t>
@@ -806,7 +836,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1327,7 +1357,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>102</v>
       </c>
@@ -1335,57 +1365,117 @@
         <v>103</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="4" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <f aca="false">COUNTIF(C5:C29,"VERIFICADO")</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <f aca="false">COUNTIF(C5:C29,"PROBABLE")</f>
-        <v>8</v>
+      <c r="F31" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <f aca="false">COUNTIF(C5:C29,"HIPÓTESIS*")</f>
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <f aca="false">COUNTIF(C5:C32,"VERIFICADO")</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <f aca="false">COUNTIF(C5:C32,"PROBABLE")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <f aca="false">COUNTIF(C5:C32,"HIPÓTESIS*")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="9" t="n">
-        <f aca="false">COUNTIF(C5:C29,"BLOQUEADO")</f>
-        <v>1</v>
+      <c r="C38" s="9" t="n">
+        <f aca="false">COUNTIF(C5:C32,"BLOQUEADO")</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
